--- a/Ticket_Analysis.xlsx
+++ b/Ticket_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Data_Analyst_Assignment\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F800A44C-B229-4687-9B63-42945CCCFC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89736BF2-0343-478D-BD67-F9C173981657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{144E5DA0-D9C2-4441-B99F-3C3A2AB694B9}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="7" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>cms_id</t>
   </si>
@@ -84,6 +84,21 @@
   </si>
   <si>
     <t>Same Hour?</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Count of Same Day?</t>
+  </si>
+  <si>
+    <t>Count of Same Hour?</t>
   </si>
 </sst>
 </file>
@@ -110,7 +125,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -118,133 +133,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -267,7 +170,7 @@
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G3" sheet="ticket"/>
   </cacheSource>
-  <cacheFields count="7">
+  <cacheFields count="10">
     <cacheField name="ticket_id " numFmtId="0">
       <sharedItems/>
     </cacheField>
@@ -275,7 +178,11 @@
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2021-08-19T16:45:00" maxDate="2021-08-21T11:09:00"/>
     </cacheField>
     <cacheField name="closed_at" numFmtId="168">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2021-08-21T17:13:00" maxDate="2021-08-22T12:33:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2021-08-21T17:13:00" maxDate="2021-08-22T12:33:00" count="2">
+        <d v="2021-08-22T12:33:00"/>
+        <d v="2021-08-21T17:13:00"/>
+      </sharedItems>
+      <fieldGroup par="9"/>
     </cacheField>
     <cacheField name="outlet_id" numFmtId="0">
       <sharedItems count="2">
@@ -284,7 +191,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="cms_id" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="c1"/>
+        <s v="c2"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Same Day?" numFmtId="0">
       <sharedItems count="2">
@@ -296,6 +206,483 @@
       <sharedItems count="1">
         <s v="No"/>
       </sharedItems>
+    </cacheField>
+    <cacheField name="Minutes (closed_at)" numFmtId="0" databaseField="0">
+      <fieldGroup base="2">
+        <rangePr groupBy="minutes" startDate="2021-08-21T17:13:00" endDate="2021-08-22T12:33:00"/>
+        <groupItems count="62">
+          <s v="&lt;21-08-2021"/>
+          <s v=":00"/>
+          <s v=":01"/>
+          <s v=":02"/>
+          <s v=":03"/>
+          <s v=":04"/>
+          <s v=":05"/>
+          <s v=":06"/>
+          <s v=":07"/>
+          <s v=":08"/>
+          <s v=":09"/>
+          <s v=":10"/>
+          <s v=":11"/>
+          <s v=":12"/>
+          <s v=":13"/>
+          <s v=":14"/>
+          <s v=":15"/>
+          <s v=":16"/>
+          <s v=":17"/>
+          <s v=":18"/>
+          <s v=":19"/>
+          <s v=":20"/>
+          <s v=":21"/>
+          <s v=":22"/>
+          <s v=":23"/>
+          <s v=":24"/>
+          <s v=":25"/>
+          <s v=":26"/>
+          <s v=":27"/>
+          <s v=":28"/>
+          <s v=":29"/>
+          <s v=":30"/>
+          <s v=":31"/>
+          <s v=":32"/>
+          <s v=":33"/>
+          <s v=":34"/>
+          <s v=":35"/>
+          <s v=":36"/>
+          <s v=":37"/>
+          <s v=":38"/>
+          <s v=":39"/>
+          <s v=":40"/>
+          <s v=":41"/>
+          <s v=":42"/>
+          <s v=":43"/>
+          <s v=":44"/>
+          <s v=":45"/>
+          <s v=":46"/>
+          <s v=":47"/>
+          <s v=":48"/>
+          <s v=":49"/>
+          <s v=":50"/>
+          <s v=":51"/>
+          <s v=":52"/>
+          <s v=":53"/>
+          <s v=":54"/>
+          <s v=":55"/>
+          <s v=":56"/>
+          <s v=":57"/>
+          <s v=":58"/>
+          <s v=":59"/>
+          <s v="&gt;22-08-2021"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Hours (closed_at)" numFmtId="0" databaseField="0">
+      <fieldGroup base="2">
+        <rangePr groupBy="hours" startDate="2021-08-21T17:13:00" endDate="2021-08-22T12:33:00"/>
+        <groupItems count="26">
+          <s v="&lt;21-08-2021"/>
+          <s v="00"/>
+          <s v="01"/>
+          <s v="02"/>
+          <s v="03"/>
+          <s v="04"/>
+          <s v="05"/>
+          <s v="06"/>
+          <s v="07"/>
+          <s v="08"/>
+          <s v="09"/>
+          <s v="10"/>
+          <s v="11"/>
+          <s v="12"/>
+          <s v="13"/>
+          <s v="14"/>
+          <s v="15"/>
+          <s v="16"/>
+          <s v="17"/>
+          <s v="18"/>
+          <s v="19"/>
+          <s v="20"/>
+          <s v="21"/>
+          <s v="22"/>
+          <s v="23"/>
+          <s v="&gt;22-08-2021"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Days (closed_at)" numFmtId="0" databaseField="0">
+      <fieldGroup base="2">
+        <rangePr groupBy="days" startDate="2021-08-21T17:13:00" endDate="2021-08-22T12:33:00"/>
+        <groupItems count="368">
+          <s v="&lt;21-08-2021"/>
+          <s v="01-Jan"/>
+          <s v="02-Jan"/>
+          <s v="03-Jan"/>
+          <s v="04-Jan"/>
+          <s v="05-Jan"/>
+          <s v="06-Jan"/>
+          <s v="07-Jan"/>
+          <s v="08-Jan"/>
+          <s v="09-Jan"/>
+          <s v="10-Jan"/>
+          <s v="11-Jan"/>
+          <s v="12-Jan"/>
+          <s v="13-Jan"/>
+          <s v="14-Jan"/>
+          <s v="15-Jan"/>
+          <s v="16-Jan"/>
+          <s v="17-Jan"/>
+          <s v="18-Jan"/>
+          <s v="19-Jan"/>
+          <s v="20-Jan"/>
+          <s v="21-Jan"/>
+          <s v="22-Jan"/>
+          <s v="23-Jan"/>
+          <s v="24-Jan"/>
+          <s v="25-Jan"/>
+          <s v="26-Jan"/>
+          <s v="27-Jan"/>
+          <s v="28-Jan"/>
+          <s v="29-Jan"/>
+          <s v="30-Jan"/>
+          <s v="31-Jan"/>
+          <s v="01-Feb"/>
+          <s v="02-Feb"/>
+          <s v="03-Feb"/>
+          <s v="04-Feb"/>
+          <s v="05-Feb"/>
+          <s v="06-Feb"/>
+          <s v="07-Feb"/>
+          <s v="08-Feb"/>
+          <s v="09-Feb"/>
+          <s v="10-Feb"/>
+          <s v="11-Feb"/>
+          <s v="12-Feb"/>
+          <s v="13-Feb"/>
+          <s v="14-Feb"/>
+          <s v="15-Feb"/>
+          <s v="16-Feb"/>
+          <s v="17-Feb"/>
+          <s v="18-Feb"/>
+          <s v="19-Feb"/>
+          <s v="20-Feb"/>
+          <s v="21-Feb"/>
+          <s v="22-Feb"/>
+          <s v="23-Feb"/>
+          <s v="24-Feb"/>
+          <s v="25-Feb"/>
+          <s v="26-Feb"/>
+          <s v="27-Feb"/>
+          <s v="28-Feb"/>
+          <s v="29-Feb"/>
+          <s v="01-Mar"/>
+          <s v="02-Mar"/>
+          <s v="03-Mar"/>
+          <s v="04-Mar"/>
+          <s v="05-Mar"/>
+          <s v="06-Mar"/>
+          <s v="07-Mar"/>
+          <s v="08-Mar"/>
+          <s v="09-Mar"/>
+          <s v="10-Mar"/>
+          <s v="11-Mar"/>
+          <s v="12-Mar"/>
+          <s v="13-Mar"/>
+          <s v="14-Mar"/>
+          <s v="15-Mar"/>
+          <s v="16-Mar"/>
+          <s v="17-Mar"/>
+          <s v="18-Mar"/>
+          <s v="19-Mar"/>
+          <s v="20-Mar"/>
+          <s v="21-Mar"/>
+          <s v="22-Mar"/>
+          <s v="23-Mar"/>
+          <s v="24-Mar"/>
+          <s v="25-Mar"/>
+          <s v="26-Mar"/>
+          <s v="27-Mar"/>
+          <s v="28-Mar"/>
+          <s v="29-Mar"/>
+          <s v="30-Mar"/>
+          <s v="31-Mar"/>
+          <s v="01-Apr"/>
+          <s v="02-Apr"/>
+          <s v="03-Apr"/>
+          <s v="04-Apr"/>
+          <s v="05-Apr"/>
+          <s v="06-Apr"/>
+          <s v="07-Apr"/>
+          <s v="08-Apr"/>
+          <s v="09-Apr"/>
+          <s v="10-Apr"/>
+          <s v="11-Apr"/>
+          <s v="12-Apr"/>
+          <s v="13-Apr"/>
+          <s v="14-Apr"/>
+          <s v="15-Apr"/>
+          <s v="16-Apr"/>
+          <s v="17-Apr"/>
+          <s v="18-Apr"/>
+          <s v="19-Apr"/>
+          <s v="20-Apr"/>
+          <s v="21-Apr"/>
+          <s v="22-Apr"/>
+          <s v="23-Apr"/>
+          <s v="24-Apr"/>
+          <s v="25-Apr"/>
+          <s v="26-Apr"/>
+          <s v="27-Apr"/>
+          <s v="28-Apr"/>
+          <s v="29-Apr"/>
+          <s v="30-Apr"/>
+          <s v="01-May"/>
+          <s v="02-May"/>
+          <s v="03-May"/>
+          <s v="04-May"/>
+          <s v="05-May"/>
+          <s v="06-May"/>
+          <s v="07-May"/>
+          <s v="08-May"/>
+          <s v="09-May"/>
+          <s v="10-May"/>
+          <s v="11-May"/>
+          <s v="12-May"/>
+          <s v="13-May"/>
+          <s v="14-May"/>
+          <s v="15-May"/>
+          <s v="16-May"/>
+          <s v="17-May"/>
+          <s v="18-May"/>
+          <s v="19-May"/>
+          <s v="20-May"/>
+          <s v="21-May"/>
+          <s v="22-May"/>
+          <s v="23-May"/>
+          <s v="24-May"/>
+          <s v="25-May"/>
+          <s v="26-May"/>
+          <s v="27-May"/>
+          <s v="28-May"/>
+          <s v="29-May"/>
+          <s v="30-May"/>
+          <s v="31-May"/>
+          <s v="01-Jun"/>
+          <s v="02-Jun"/>
+          <s v="03-Jun"/>
+          <s v="04-Jun"/>
+          <s v="05-Jun"/>
+          <s v="06-Jun"/>
+          <s v="07-Jun"/>
+          <s v="08-Jun"/>
+          <s v="09-Jun"/>
+          <s v="10-Jun"/>
+          <s v="11-Jun"/>
+          <s v="12-Jun"/>
+          <s v="13-Jun"/>
+          <s v="14-Jun"/>
+          <s v="15-Jun"/>
+          <s v="16-Jun"/>
+          <s v="17-Jun"/>
+          <s v="18-Jun"/>
+          <s v="19-Jun"/>
+          <s v="20-Jun"/>
+          <s v="21-Jun"/>
+          <s v="22-Jun"/>
+          <s v="23-Jun"/>
+          <s v="24-Jun"/>
+          <s v="25-Jun"/>
+          <s v="26-Jun"/>
+          <s v="27-Jun"/>
+          <s v="28-Jun"/>
+          <s v="29-Jun"/>
+          <s v="30-Jun"/>
+          <s v="01-Jul"/>
+          <s v="02-Jul"/>
+          <s v="03-Jul"/>
+          <s v="04-Jul"/>
+          <s v="05-Jul"/>
+          <s v="06-Jul"/>
+          <s v="07-Jul"/>
+          <s v="08-Jul"/>
+          <s v="09-Jul"/>
+          <s v="10-Jul"/>
+          <s v="11-Jul"/>
+          <s v="12-Jul"/>
+          <s v="13-Jul"/>
+          <s v="14-Jul"/>
+          <s v="15-Jul"/>
+          <s v="16-Jul"/>
+          <s v="17-Jul"/>
+          <s v="18-Jul"/>
+          <s v="19-Jul"/>
+          <s v="20-Jul"/>
+          <s v="21-Jul"/>
+          <s v="22-Jul"/>
+          <s v="23-Jul"/>
+          <s v="24-Jul"/>
+          <s v="25-Jul"/>
+          <s v="26-Jul"/>
+          <s v="27-Jul"/>
+          <s v="28-Jul"/>
+          <s v="29-Jul"/>
+          <s v="30-Jul"/>
+          <s v="31-Jul"/>
+          <s v="01-Aug"/>
+          <s v="02-Aug"/>
+          <s v="03-Aug"/>
+          <s v="04-Aug"/>
+          <s v="05-Aug"/>
+          <s v="06-Aug"/>
+          <s v="07-Aug"/>
+          <s v="08-Aug"/>
+          <s v="09-Aug"/>
+          <s v="10-Aug"/>
+          <s v="11-Aug"/>
+          <s v="12-Aug"/>
+          <s v="13-Aug"/>
+          <s v="14-Aug"/>
+          <s v="15-Aug"/>
+          <s v="16-Aug"/>
+          <s v="17-Aug"/>
+          <s v="18-Aug"/>
+          <s v="19-Aug"/>
+          <s v="20-Aug"/>
+          <s v="21-Aug"/>
+          <s v="22-Aug"/>
+          <s v="23-Aug"/>
+          <s v="24-Aug"/>
+          <s v="25-Aug"/>
+          <s v="26-Aug"/>
+          <s v="27-Aug"/>
+          <s v="28-Aug"/>
+          <s v="29-Aug"/>
+          <s v="30-Aug"/>
+          <s v="31-Aug"/>
+          <s v="01-Sep"/>
+          <s v="02-Sep"/>
+          <s v="03-Sep"/>
+          <s v="04-Sep"/>
+          <s v="05-Sep"/>
+          <s v="06-Sep"/>
+          <s v="07-Sep"/>
+          <s v="08-Sep"/>
+          <s v="09-Sep"/>
+          <s v="10-Sep"/>
+          <s v="11-Sep"/>
+          <s v="12-Sep"/>
+          <s v="13-Sep"/>
+          <s v="14-Sep"/>
+          <s v="15-Sep"/>
+          <s v="16-Sep"/>
+          <s v="17-Sep"/>
+          <s v="18-Sep"/>
+          <s v="19-Sep"/>
+          <s v="20-Sep"/>
+          <s v="21-Sep"/>
+          <s v="22-Sep"/>
+          <s v="23-Sep"/>
+          <s v="24-Sep"/>
+          <s v="25-Sep"/>
+          <s v="26-Sep"/>
+          <s v="27-Sep"/>
+          <s v="28-Sep"/>
+          <s v="29-Sep"/>
+          <s v="30-Sep"/>
+          <s v="01-Oct"/>
+          <s v="02-Oct"/>
+          <s v="03-Oct"/>
+          <s v="04-Oct"/>
+          <s v="05-Oct"/>
+          <s v="06-Oct"/>
+          <s v="07-Oct"/>
+          <s v="08-Oct"/>
+          <s v="09-Oct"/>
+          <s v="10-Oct"/>
+          <s v="11-Oct"/>
+          <s v="12-Oct"/>
+          <s v="13-Oct"/>
+          <s v="14-Oct"/>
+          <s v="15-Oct"/>
+          <s v="16-Oct"/>
+          <s v="17-Oct"/>
+          <s v="18-Oct"/>
+          <s v="19-Oct"/>
+          <s v="20-Oct"/>
+          <s v="21-Oct"/>
+          <s v="22-Oct"/>
+          <s v="23-Oct"/>
+          <s v="24-Oct"/>
+          <s v="25-Oct"/>
+          <s v="26-Oct"/>
+          <s v="27-Oct"/>
+          <s v="28-Oct"/>
+          <s v="29-Oct"/>
+          <s v="30-Oct"/>
+          <s v="31-Oct"/>
+          <s v="01-Nov"/>
+          <s v="02-Nov"/>
+          <s v="03-Nov"/>
+          <s v="04-Nov"/>
+          <s v="05-Nov"/>
+          <s v="06-Nov"/>
+          <s v="07-Nov"/>
+          <s v="08-Nov"/>
+          <s v="09-Nov"/>
+          <s v="10-Nov"/>
+          <s v="11-Nov"/>
+          <s v="12-Nov"/>
+          <s v="13-Nov"/>
+          <s v="14-Nov"/>
+          <s v="15-Nov"/>
+          <s v="16-Nov"/>
+          <s v="17-Nov"/>
+          <s v="18-Nov"/>
+          <s v="19-Nov"/>
+          <s v="20-Nov"/>
+          <s v="21-Nov"/>
+          <s v="22-Nov"/>
+          <s v="23-Nov"/>
+          <s v="24-Nov"/>
+          <s v="25-Nov"/>
+          <s v="26-Nov"/>
+          <s v="27-Nov"/>
+          <s v="28-Nov"/>
+          <s v="29-Nov"/>
+          <s v="30-Nov"/>
+          <s v="01-Dec"/>
+          <s v="02-Dec"/>
+          <s v="03-Dec"/>
+          <s v="04-Dec"/>
+          <s v="05-Dec"/>
+          <s v="06-Dec"/>
+          <s v="07-Dec"/>
+          <s v="08-Dec"/>
+          <s v="09-Dec"/>
+          <s v="10-Dec"/>
+          <s v="11-Dec"/>
+          <s v="12-Dec"/>
+          <s v="13-Dec"/>
+          <s v="14-Dec"/>
+          <s v="15-Dec"/>
+          <s v="16-Dec"/>
+          <s v="17-Dec"/>
+          <s v="18-Dec"/>
+          <s v="19-Dec"/>
+          <s v="20-Dec"/>
+          <s v="21-Dec"/>
+          <s v="22-Dec"/>
+          <s v="23-Dec"/>
+          <s v="24-Dec"/>
+          <s v="25-Dec"/>
+          <s v="26-Dec"/>
+          <s v="27-Dec"/>
+          <s v="28-Dec"/>
+          <s v="29-Dec"/>
+          <s v="30-Dec"/>
+          <s v="31-Dec"/>
+          <s v="&gt;22-08-2021"/>
+        </groupItems>
+      </fieldGroup>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -311,18 +698,18 @@
   <r>
     <s v="t1"/>
     <d v="2021-08-19T16:45:00"/>
-    <d v="2021-08-22T12:33:00"/>
     <x v="0"/>
-    <s v="c1"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
   </r>
   <r>
     <s v="t1"/>
     <d v="2021-08-21T11:09:00"/>
-    <d v="2021-08-21T17:13:00"/>
     <x v="1"/>
-    <s v="c2"/>
+    <x v="1"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
   </r>
@@ -330,12 +717,25 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EAB0B2B1-49B6-443C-9647-D819D732CCB0}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EAB0B2B1-49B6-443C-9647-D819D732CCB0}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="168" showAll="0"/>
-    <pivotField numFmtId="168" showAll="0"/>
+    <pivotField numFmtId="168" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="3">
         <item x="0"/>
@@ -343,16 +743,527 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
+    <pivotField dataField="1" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="63">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="27">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
+  <rowFields count="2">
+    <field x="3"/>
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of Same Day?" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Count of Same Hour?" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -682,101 +1593,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72C3358-E743-4C57-AE25-C3A21E40C519}">
-  <dimension ref="A3:C20"/>
+  <dimension ref="A3:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
+      <c r="A5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -788,8 +1677,8 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" customWidth="1"/>
@@ -799,10 +1688,10 @@
       <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D1" t="s">
@@ -822,10 +1711,10 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>44427.697916666664</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>44430.522916666669</v>
       </c>
       <c r="D2" t="s">
@@ -847,10 +1736,10 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>44429.464583333334</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>44429.717361111114</v>
       </c>
       <c r="D3" t="s">
@@ -879,7 +1768,7 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="24.109375" customWidth="1"/>
   </cols>
@@ -888,7 +1777,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -902,7 +1791,7 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>44429.55972222222</v>
       </c>
       <c r="C2">
@@ -917,7 +1806,7 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>44430.416666666664</v>
       </c>
       <c r="C3">
